--- a/config/yunying/itemexchange.xlsx
+++ b/config/yunying/itemexchange.xlsx
@@ -1918,7 +1918,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>金貨*1000</t>
+          <t>金币*1000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ダイヤガチャ券*1</t>
+          <t>钻石扭蛋券*1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>スタミナ*1</t>
+          <t>耐力*1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>スッキリソーダ*1</t>
+          <t>苏打水*1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>初級好感度箱*1</t>
+          <t>初级好感度箱*1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>突破素材抽選箱*1</t>
+          <t>突破素材抽选箱*1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>高級強化コイン*1</t>
+          <t>高级强化硬币*1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>紫潜能コア*1</t>
+          <t>紫色潜能核心*1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>装飾コア*1</t>
+          <t>装饰核心*1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>特権コイン*1</t>
+          <t>特权硬币*1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>不思議なカプセル*1</t>
+          <t>神奇胶囊*1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>紫超進化石*1</t>
+          <t>紫超进化石*1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>橙超進化石*1</t>
+          <t>橙超进化石*1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>クッキー*1</t>
+          <t>饼干*1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>聖夜の鈴*1</t>
+          <t>圣诞夜之铃*1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>橙ルーン選定箱*1</t>
+          <t>橙符文选定箱*1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>橙チップ選定箱*1</t>
+          <t>橙色芯片选定箱*1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>クリスマス(2025)限定称号*1</t>
+          <t>圣诞节（2025）限定称号*1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>雪の聖夜*1</t>
+          <t>雪之圣夜*1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ナギサクリスマス</t>
+          <t>渚圣诞节</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>ルミナクリスマス</t>
+          <t>鲁米纳圣诞节</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>ミホクリスマス</t>
+          <t>美穗圣诞节</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="G349" s="1" t="inlineStr">
         <is>
-          <t>神原千雪のカケラ</t>
+          <t>神原千雪的碎片</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="G350" s="1" t="inlineStr">
         <is>
-          <t>千寻のカケラ</t>
+          <t>千寻的碎片</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="G351" s="1" t="inlineStr">
         <is>
-          <t>希恩のカケラ</t>
+          <t>希恩的碎片</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="G352" s="1" t="inlineStr">
         <is>
-          <t>真琴のカケラ</t>
+          <t>真琴的碎片</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="G353" s="1" t="inlineStr">
         <is>
-          <t>洛娜のカケラ</t>
+          <t>洛娜的碎片</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="G354" s="1" t="inlineStr">
         <is>
-          <t>纪汐のカケラ</t>
+          <t>纪汐的碎片</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="G355" s="1" t="inlineStr">
         <is>
-          <t>加莉娜のカケラ</t>
+          <t>加莉娜的碎片</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G356" s="1" t="inlineStr">
         <is>
-          <t>咲初小藤のカケラ</t>
+          <t>咲初小藤的碎片</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G357" s="1" t="inlineStr">
         <is>
-          <t>南丁格尔のカケラ</t>
+          <t>南丁格尔的碎片</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G358" s="1" t="inlineStr">
         <is>
-          <t>火野のカケラ</t>
+          <t>火野的碎片</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="G359" s="1" t="inlineStr">
         <is>
-          <t>紫樱のカケラ</t>
+          <t>紫樱花的碎片</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="G360" s="1" t="inlineStr">
         <is>
-          <t>露琪亚のカケラ</t>
+          <t>露琪亚的碎片</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="G361" s="1" t="inlineStr">
         <is>
-          <t>卡诺恩のカケラ</t>
+          <t>卡诺恩的碎片</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="G362" s="1" t="inlineStr">
         <is>
-          <t>凤天盈のカケラ</t>
+          <t>凤天盈的碎片</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="G363" s="1" t="inlineStr">
         <is>
-          <t>美穗のカケラ</t>
+          <t>美穗的碎片</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="G364" s="1" t="inlineStr">
         <is>
-          <t>米朵のカケラ</t>
+          <t>米朵的碎片</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G365" s="1" t="inlineStr">
         <is>
-          <t>青羽のカケラ</t>
+          <t>青羽的碎片</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="G366" s="1" t="inlineStr">
         <is>
-          <t>礼奈のカケラ</t>
+          <t>礼奈的碎片</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="G368" s="1" t="inlineStr">
         <is>
-          <t>200翡翠の御守</t>
+          <t>200翡翠翡翠</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G369" s="1" t="inlineStr">
         <is>
-          <t>201雪光の御守</t>
+          <t>201雪光之神</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G370" s="1" t="inlineStr">
         <is>
-          <t>202水晶の御守</t>
+          <t>202水晶之神</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="G371" s="1" t="inlineStr">
         <is>
-          <t>203真紅の御守</t>
+          <t>203《红色的守护者》</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="G373" s="1" t="inlineStr">
         <is>
-          <t>205閃光の御守</t>
+          <t>205闪光的守护者</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
-          <t>ダイヤ*388   交換   护符能量精华*50</t>
+          <t>钻石*388交换护符能力精华*50</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="G375" s="1" t="inlineStr">
         <is>
-          <t>200翡翠の御守</t>
+          <t>200翡翠翡翠</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="G376" s="1" t="inlineStr">
         <is>
-          <t>201雪光の御守</t>
+          <t>201雪光之神</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="G377" s="1" t="inlineStr">
         <is>
-          <t>202水晶の御守</t>
+          <t>202水晶之神</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="G378" s="1" t="inlineStr">
         <is>
-          <t>203真紅の御守</t>
+          <t>203《红色的守护者》</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="G380" s="1" t="inlineStr">
         <is>
-          <t>205閃光の御守</t>
+          <t>205闪光的守护者</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="G382" s="1" t="inlineStr">
         <is>
-          <t>210翡翠の耳飾り</t>
+          <t>210翡翠耳环</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="G383" s="1" t="inlineStr">
         <is>
-          <t>211蒼月の耳飾り</t>
+          <t>211月亮的耳朵</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="G384" s="1" t="inlineStr">
         <is>
-          <t>212星羽の耳飾り</t>
+          <t>212星星的耳朵</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="G385" s="1" t="inlineStr">
         <is>
-          <t>213天翼の耳飾り</t>
+          <t>213天翼耳环</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="G386" s="1" t="inlineStr">
         <is>
-          <t>214澄海の耳飾り</t>
+          <t>214《澄海的耳朵》</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="G387" s="1" t="inlineStr">
         <is>
-          <t>215高貴な耳飾り</t>
+          <t>215美丽的耳环</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="G388" s="4" t="inlineStr">
         <is>
-          <t>ダイヤ*388   交換   耳环能量精华*50</t>
+          <t>钻石*388交换耳环能量精华*50</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="G389" s="1" t="inlineStr">
         <is>
-          <t>210翡翠の耳飾り</t>
+          <t>210翡翠耳环</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="G390" s="1" t="inlineStr">
         <is>
-          <t>211蒼月の耳飾り</t>
+          <t>211月亮的耳朵</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G391" s="1" t="inlineStr">
         <is>
-          <t>212星羽の耳飾り</t>
+          <t>212星星的耳朵</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="G392" s="1" t="inlineStr">
         <is>
-          <t>213天翼の耳飾り</t>
+          <t>213天翼耳环</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G393" s="1" t="inlineStr">
         <is>
-          <t>214澄海の耳飾り</t>
+          <t>214《澄海的耳朵》</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="G394" s="1" t="inlineStr">
         <is>
-          <t>215高貴な耳飾り</t>
+          <t>215美丽的耳环</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="G396" s="1" t="inlineStr">
         <is>
-          <t>220クローバーの指輪</t>
+          <t>220三叶草戒指</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="G397" s="1" t="inlineStr">
         <is>
-          <t>221精巧な指輪</t>
+          <t>221精致的戒指</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="G398" s="1" t="inlineStr">
         <is>
-          <t>222星月の指輪</t>
+          <t>222星月戒指</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G399" s="1" t="inlineStr">
         <is>
-          <t>223臙脂の指輪</t>
+          <t>223胭脂戒指</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="G400" s="1" t="inlineStr">
         <is>
-          <t>224澄海の指輪</t>
+          <t>第224章大海之戒</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="G401" s="1" t="inlineStr">
         <is>
-          <t>225月影の指輪</t>
+          <t>225月影戒指</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="G402" s="4" t="inlineStr">
         <is>
-          <t>ダイヤ*388   交換   戒指能量精华*50</t>
+          <t>钻石*388交换戒指能力精华*50</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="G403" s="1" t="inlineStr">
         <is>
-          <t>220クローバーの指輪</t>
+          <t>220三叶草戒指</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="G404" s="1" t="inlineStr">
         <is>
-          <t>221精巧な指輪</t>
+          <t>221精致的戒指</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="G405" s="1" t="inlineStr">
         <is>
-          <t>222星月の指輪</t>
+          <t>222星月戒指</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="G406" s="1" t="inlineStr">
         <is>
-          <t>223臙脂の指輪</t>
+          <t>223胭脂戒指</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="G407" s="1" t="inlineStr">
         <is>
-          <t>224澄海の指輪</t>
+          <t>第224章大海之戒</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G408" s="1" t="inlineStr">
         <is>
-          <t>225月影の指輪</t>
+          <t>225月影戒指</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="G410" s="1" t="inlineStr">
         <is>
-          <t>230クローバーの首飾り</t>
+          <t>230三叶草项链</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="G411" s="1" t="inlineStr">
         <is>
-          <t>231雪光の首飾り</t>
+          <t>231雪花项链</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="G412" s="1" t="inlineStr">
         <is>
-          <t>232幻影の首飾り</t>
+          <t>232幽灵项链</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="G413" s="1" t="inlineStr">
         <is>
-          <t>233太陽の首飾り</t>
+          <t>233太阳的项链</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="G414" s="1" t="inlineStr">
         <is>
-          <t>234澄海のの首飾り</t>
+          <t>234澄海的项链</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="G415" s="1" t="inlineStr">
         <is>
-          <t>235輝星の首飾り</t>
+          <t>235星星的项链</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="G416" s="4" t="inlineStr">
         <is>
-          <t>ダイヤ*388   交換   项链能量精华*50</t>
+          <t>钻石*388交换项炼能力精华*50</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="G417" s="1" t="inlineStr">
         <is>
-          <t>230クローバーの首飾り</t>
+          <t>230三叶草项链</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="G418" s="1" t="inlineStr">
         <is>
-          <t>231雪光の首飾り</t>
+          <t>231雪花项链</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G419" s="1" t="inlineStr">
         <is>
-          <t>232幻影の首飾り</t>
+          <t>232幽灵项链</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="G420" s="1" t="inlineStr">
         <is>
-          <t>233太陽の首飾り</t>
+          <t>233太阳的项链</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="G421" s="1" t="inlineStr">
         <is>
-          <t>234澄海のの首飾り</t>
+          <t>234澄海的项链</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="G422" s="1" t="inlineStr">
         <is>
-          <t>235輝星の首飾り</t>
+          <t>235星星的项链</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="G424" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="G425" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="G426" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="G427" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G428" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   炎帝のカケラ*5</t>
+          <t>紫色优惠券*6兑换炎帝碎片*5</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="G429" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   班吉拉斯のカケラ*5</t>
+          <t>紫色优惠券*6交换班吉拉德斯碎片*5</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="G430" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   戴鲁比のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换戴鲁比的碎片*3</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="G431" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   可可多拉のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3可交换多拉碎片*3</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="G432" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   小锯鳄のカケラ*3</t>
+          <t>蓝色优惠券*5交换小鋸鳄碎片*3</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="G433" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   雪笠怪のカケラ*3</t>
+          <t>蓝色优惠券*5交换雪笠怪碎片*3</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="G434" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   搬运小匠のカケラ*3</t>
+          <t>蓝色优惠券*5交换搬运小匠碎片*3</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="G435" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   绵绵泡芙のカケラ*3</t>
+          <t>蓝色优惠券*5交换棉花泡芙碎片*3</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="G436" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G437" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="G438" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="G439" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="G440" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G441" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="G442" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="G443" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G444" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>中級強化石*1</t>
+          <t>中级强化石*1</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>肉缶詰*1</t>
+          <t>肉罐头*1</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>一般強化コイン*1</t>
+          <t>一般强化硬币*1</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>金の鍵*2</t>
+          <t>金钥匙*2</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>ハッカーツール*1</t>
+          <t>黑客工具*1</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>開放の手*1</t>
+          <t>开放之手*1</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>豪華弁当*1</t>
+          <t>豪华午餐*1</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>天賦コイン*1</t>
+          <t>天赋硬币*1</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>上級好感度箱*1</t>
+          <t>上级好感度箱*1</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>不思議なカプセル*10</t>
+          <t>神奇胶囊*10</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>万能カケラ*5</t>
+          <t>万能片*5</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ*388</t>
+          <t>钻石*388</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -17603,7 +17603,7 @@
       <c r="F458" s="6" t="n"/>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>シオンクリスマス*1</t>
+          <t>锡安圣诞节*1</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -17644,7 +17644,7 @@
       <c r="F459" s="6" t="n"/>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>セイラクリスマス*1</t>
+          <t>塞拉圣诞节*1</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -17685,7 +17685,7 @@
       <c r="F460" s="6" t="n"/>
       <c r="G460" t="inlineStr">
         <is>
-          <t>マコクリスマス*1</t>
+          <t>真正的圣诞节*1</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -17723,7 +17723,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>クリスマス*1</t>
+          <t>圣诞节*1</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="G464" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="G465" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="G466" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="G467" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="G468" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   独角犀牛のカケラ*5</t>
+          <t>紫色优惠券*6兑换独角犀牛*5</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="G469" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   赫拉克罗斯のカケラ*5</t>
+          <t>紫优惠券*6交换放过克罗斯的碎片*5</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="G470" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   飞天螳螂のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换飞天螳螂股份*3</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="G471" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   凯西のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换凯西的碎片*3</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="G472" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   喷嚏熊のカケラ*3</t>
+          <t>蓝色优惠券*5兑换喷嚏熊碎片*3</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="G473" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   冰雪龙のカケラ*3</t>
+          <t>蓝色优惠券*5兑换冰雪龙碎片*3</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="G474" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   无畏小子のカケラ*3</t>
+          <t>蓝色优惠券*5交换无畏小孩的碎片*3</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="G475" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="G476" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="G477" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="G478" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="G479" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="G480" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="G481" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="G482" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="G484" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="G486" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="G487" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="G488" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="G489" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="G490" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   懒人獭のカケラ*5</t>
+          <t>紫色优惠券*6兑换懒人獭碎片*5</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="G491" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   火焰鸟のカケラ*5</t>
+          <t>紫色优惠券*6交换火焰鸟碎片*5</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="G492" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   鸭嘴宝宝のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3兑换鸭嘴宝宝碎片*3</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G493" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   阿勃梭鲁のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3兑换阿勃梭鲁碎片*3</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G494" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   哈力栗のカケラ*3</t>
+          <t>蓝色优惠券*5兑换哈力栗子片*3</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="G495" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   草苗龟のカケラ*3</t>
+          <t>蓝色优惠券*5交换草苗龟碎片*3</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="G496" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   迷你冰のカケラ*3</t>
+          <t>蓝色优惠券*5交换迷你冰块*3</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="G497" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   瓦斯弹のカケラ*3</t>
+          <t>蓝色优惠券*5交换瓦斯弹碎片*3</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -19195,7 +19195,7 @@
       </c>
       <c r="G498" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="G499" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="G500" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="G501" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -19363,7 +19363,7 @@
       </c>
       <c r="G502" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="G503" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G504" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="G505" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -19531,7 +19531,7 @@
       </c>
       <c r="G506" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="G510" s="1" t="inlineStr">
         <is>
-          <t>銀の首飾り*1</t>
+          <t>银项链*1</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="G511" s="1" t="inlineStr">
         <is>
-          <t>紫·強化*1</t>
+          <t>紫色强化*1</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="G512" s="1" t="inlineStr">
         <is>
-          <t>ガチャ券*1</t>
+          <t>扭蛋券*1</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="G513" s="1" t="inlineStr">
         <is>
-          <t>饰品ガチャ券*1</t>
+          <t>饰品转蛋券*1</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="G514" s="5" t="inlineStr">
         <is>
-          <t>探査機ガチャ券*1</t>
+          <t>探测器游戏券*1</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="G516" s="5" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム*1</t>
+          <t>装饰星星物品*1</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="G518" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G520" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G522" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G523" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="G524" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G525" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="G526" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   急冻鸟のカケラ*5</t>
+          <t>紫色优惠券*6兑换急冻鸟碎片*5</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="G527" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   几何雪花のカケラ*5</t>
+          <t>紫色优惠券*6兑换几何雪花碎片*5</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G528" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   鬼斯のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换鬼斯碎片*3</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="G529" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   夜巡灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3兑换夜巡灵碎片*3</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="G530" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   雪童子のカケラ*3</t>
+          <t>蓝色优惠券*5交换雪童子的碎片*3</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="G531" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   石丸子のカケラ*3</t>
+          <t>蓝色优惠券*5交换石头丸子碎片*3</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="G532" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   大舌舔のカケラ*3</t>
+          <t>蓝色优惠券*5交换大舌头舔的碎片*3</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="G533" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   大比鸟のカケラ*3</t>
+          <t>蓝色优惠券*5兑换大比鸟碎片*3</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="G534" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="G535" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="G536" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="G537" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="G538" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G539" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="G540" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G541" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="G542" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="G544" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="G545" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="G546" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="G547" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="G548" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   双斧战龙のカケラ*5</t>
+          <t>紫色优惠券*6兑换双斧战龙碎片*5</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="G549" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   巨钳螳螂のカケラ*5</t>
+          <t>紫色优惠券*6兑换巨形螳螂股份*5</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="G550" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   大钢蛇のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3兑换大钢蛇碎片*3</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -21304,7 +21304,7 @@
       </c>
       <c r="G551" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   夜巡灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3兑换夜巡灵碎片*3</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="G552" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   菊叶草のカケラ*3</t>
+          <t>蓝色优惠券*5交换菊花叶子草碎片*3</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="G553" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   胖甜妮のカケラ*3</t>
+          <t>蓝色优惠券*5兑换胖甜妮的碎片*3</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="G554" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   怪力のカケラ*3</t>
+          <t>蓝色优惠券*5交换怪力碎片*3</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="G555" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   无畏小子のカケラ*3</t>
+          <t>蓝色优惠券*5交换无畏小孩的碎片*3</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="G556" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="G557" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="G558" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -21640,7 +21640,7 @@
       </c>
       <c r="G559" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="G560" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="G561" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="G562" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -21850,7 +21850,7 @@
       </c>
       <c r="G564" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="G565" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="G567" s="1" t="inlineStr">
         <is>
-          <t>お出かけパック*1</t>
+          <t>外出包*1</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="G568" s="1" t="inlineStr">
         <is>
-          <t>フレーム*1</t>
+          <t>框架*1</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="G569" s="1" t="inlineStr">
         <is>
-          <t>柳草パック*1</t>
+          <t>柳草面膜*1</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="G571" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="G572" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="G573" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="G574" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="G575" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="G577" s="1" t="inlineStr">
         <is>
-          <t>GWフレーム*1</t>
+          <t>GW帧*1</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="G579" s="1" t="inlineStr">
         <is>
-          <t>スパイ万能欠片*1</t>
+          <t>间谍万能碎片*1</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G580" s="1" t="inlineStr">
         <is>
-          <t>銀の首飾り*1</t>
+          <t>银项链*1</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="G581" s="1" t="inlineStr">
         <is>
-          <t>紫·強化*1</t>
+          <t>紫色强化*1</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="G585" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="G586" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="G588" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="G589" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -22786,7 +22786,7 @@
       </c>
       <c r="G590" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="G591" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="G592" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   闪电鸟のカケラ*5</t>
+          <t>紫色优惠券*6兑换闪电鸟碎片*5</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="G593" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   独剑鞘のカケラ*5</t>
+          <t>紫色优惠券*6兑换独剑鞘碎片*5</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="G594" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   鬼斯のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换鬼斯碎片*3</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="G595" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   音波龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换声波龙碎片*3</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="G596" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   螺钉地鼠のカケラ*3</t>
+          <t>蓝色优惠券*5交换螺钉地鼠碎片*3</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="G597" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   歌德宝宝のカケラ*3</t>
+          <t>蓝色优惠券*5兑换歌德宝宝的碎片*3</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="G598" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   齿轮儿のカケラ*3</t>
+          <t>蓝色优惠券*5交换齿轮儿碎片*3</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="G599" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   雪童子のカケラ*3</t>
+          <t>蓝色优惠券*5交换雪童子的碎片*3</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="G600" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="G601" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="G602" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="G603" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -23374,7 +23374,7 @@
       </c>
       <c r="G604" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="G605" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="G606" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="G607" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="G608" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="G609" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -23629,7 +23629,7 @@
       </c>
       <c r="G611" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -23671,7 +23671,7 @@
       </c>
       <c r="G612" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="G613" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="G614" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="G615" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -23842,7 +23842,7 @@
       </c>
       <c r="G617" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="G618" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -23926,7 +23926,7 @@
       </c>
       <c r="G619" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="G620" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -24010,7 +24010,7 @@
       </c>
       <c r="G621" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   独角犀牛*5</t>
+          <t>紫色优惠券*6兑换独角犀牛*5</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="G622" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="G623" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -24136,7 +24136,7 @@
       </c>
       <c r="G624" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -24178,7 +24178,7 @@
       </c>
       <c r="G625" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="G626" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="G627" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="G628" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="G629" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="G630" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="G631" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="G632" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="G633" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="G634" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="G635" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="G636" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -24682,7 +24682,7 @@
       </c>
       <c r="G637" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="G638" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -24769,7 +24769,7 @@
       </c>
       <c r="G640" s="4" t="inlineStr">
         <is>
-          <t>こどもの日フレーム*1</t>
+          <t>儿童节框架*1</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="G641" s="4" t="inlineStr">
         <is>
-          <t>こどもの日パック</t>
+          <t>儿童节包</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="G642" s="4" t="inlineStr">
         <is>
-          <t>こどもの日称号*1</t>
+          <t>儿童节称号*1</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="G643" s="4" t="inlineStr">
         <is>
-          <t>こどもの日アイコン*1</t>
+          <t>儿童节图标*1</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="G644" s="4" t="inlineStr">
         <is>
-          <t>こどもの日アイコン2*1</t>
+          <t>儿童节图标2*1</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="G645" s="4" t="inlineStr">
         <is>
-          <t>こどもの日アイコン2*1</t>
+          <t>儿童节图标2*1</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="G646" s="4" t="inlineStr">
         <is>
-          <t>こどもの日アイコン2*1</t>
+          <t>儿童节图标2*1</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -25147,7 +25147,7 @@
       </c>
       <c r="G649" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="G650" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="G652" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -25276,7 +25276,7 @@
       </c>
       <c r="G653" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="G654" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="G655" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="G656" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G658" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -25489,7 +25489,7 @@
       </c>
       <c r="G659" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="G660" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="G661" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -25615,7 +25615,7 @@
       </c>
       <c r="G662" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷吉斯奇鲁*5</t>
+          <t>紫色优惠券*6兑换雷吉斯奇鲁*5</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="G663" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="G664" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="G665" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -25783,7 +25783,7 @@
       </c>
       <c r="G666" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G667" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="G668" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -25909,7 +25909,7 @@
       </c>
       <c r="G669" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -25951,7 +25951,7 @@
       </c>
       <c r="G670" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="G671" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="G672" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="G673" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="G674" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="G675" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="G676" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -26287,7 +26287,7 @@
       </c>
       <c r="G678" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -26329,7 +26329,7 @@
       </c>
       <c r="G679" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -26374,7 +26374,7 @@
       </c>
       <c r="G681" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -26416,7 +26416,7 @@
       </c>
       <c r="G682" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -26458,7 +26458,7 @@
       </c>
       <c r="G683" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -26500,7 +26500,7 @@
       </c>
       <c r="G684" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -26542,7 +26542,7 @@
       </c>
       <c r="G685" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G687" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -26629,7 +26629,7 @@
       </c>
       <c r="G688" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="G689" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="G690" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="G691" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷吉斯奇鲁*5</t>
+          <t>紫色优惠券*6兑换雷吉斯奇鲁*5</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -26797,7 +26797,7 @@
       </c>
       <c r="G692" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="G693" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="G694" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -26923,7 +26923,7 @@
       </c>
       <c r="G695" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G696" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="G697" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="G698" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="G699" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="G700" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="G701" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -27217,7 +27217,7 @@
       </c>
       <c r="G702" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="G703" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -27301,7 +27301,7 @@
       </c>
       <c r="G704" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -27343,7 +27343,7 @@
       </c>
       <c r="G705" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G706" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="G707" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -27469,7 +27469,7 @@
       </c>
       <c r="G708" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="G710" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="G711" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -27598,7 +27598,7 @@
       </c>
       <c r="G712" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="G713" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="G714" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G716" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -27769,7 +27769,7 @@
       </c>
       <c r="G717" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -27811,7 +27811,7 @@
       </c>
       <c r="G718" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -27853,7 +27853,7 @@
       </c>
       <c r="G719" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -27895,7 +27895,7 @@
       </c>
       <c r="G720" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷吉斯奇鲁*5</t>
+          <t>紫色优惠券*6兑换雷吉斯奇鲁*5</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="G721" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="G722" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="G723" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -28063,7 +28063,7 @@
       </c>
       <c r="G724" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G725" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -28147,7 +28147,7 @@
       </c>
       <c r="G726" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="G727" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="G728" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="G729" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="G730" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -28357,7 +28357,7 @@
       </c>
       <c r="G731" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="G732" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="G733" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="G734" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G735" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="G736" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="G737" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="G739" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="G740" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="G741" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -28780,7 +28780,7 @@
       </c>
       <c r="G742" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="G743" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G745" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="G746" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="G747" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="G748" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="G749" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷吉斯奇鲁*5</t>
+          <t>紫色优惠券*6兑换雷吉斯奇鲁*5</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -29077,7 +29077,7 @@
       </c>
       <c r="G750" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -29119,7 +29119,7 @@
       </c>
       <c r="G751" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="G752" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -29203,7 +29203,7 @@
       </c>
       <c r="G753" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G754" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -29287,7 +29287,7 @@
       </c>
       <c r="G755" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="G756" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="G757" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="G758" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -29455,7 +29455,7 @@
       </c>
       <c r="G759" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -29497,7 +29497,7 @@
       </c>
       <c r="G760" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="G761" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -29581,7 +29581,7 @@
       </c>
       <c r="G762" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="G763" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G764" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="G765" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -29749,7 +29749,7 @@
       </c>
       <c r="G766" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -29986,7 +29986,7 @@
       </c>
       <c r="G774" s="4" t="inlineStr">
         <is>
-          <t>布尔美丽の信物</t>
+          <t>布尔美丽的信物</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -30028,7 +30028,7 @@
       </c>
       <c r="G775" s="1" t="inlineStr">
         <is>
-          <t>S仲間選択宝箱</t>
+          <t>S伙伴选择宝箱</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -30070,7 +30070,7 @@
       </c>
       <c r="G776" s="1" t="inlineStr">
         <is>
-          <t>装飾覚醒選択宝箱</t>
+          <t>装饰觉醒选择宝箱</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -30154,7 +30154,7 @@
       </c>
       <c r="G778" s="1" t="inlineStr">
         <is>
-          <t>ダイヤ</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -30228,7 +30228,7 @@
       </c>
       <c r="G780" s="5" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム</t>
+          <t>装饰星星项目</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="G781" s="5" t="inlineStr">
         <is>
-          <t>紫·探査機宝箱</t>
+          <t>紫色探测器宝箱</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="G782" s="1" t="inlineStr">
         <is>
-          <t>天賦Pt</t>
+          <t>天赋Pt</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -30354,7 +30354,7 @@
       </c>
       <c r="G783" s="1" t="inlineStr">
         <is>
-          <t>金貨</t>
+          <t>金币</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="G785" s="1" t="inlineStr">
         <is>
-          <t>強化薬</t>
+          <t>强化药</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -30480,7 +30480,7 @@
       </c>
       <c r="G786" s="1" t="inlineStr">
         <is>
-          <t>紫·装備強化アイテム</t>
+          <t>紫色装备强化道具</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="G788" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -30567,7 +30567,7 @@
       </c>
       <c r="G789" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="G790" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G791" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -30693,7 +30693,7 @@
       </c>
       <c r="G792" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="G794" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -30775,7 +30775,7 @@
       </c>
       <c r="G795" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -30812,7 +30812,7 @@
       </c>
       <c r="G796" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="G797" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="G798" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷吉斯奇鲁*5</t>
+          <t>紫色优惠券*6兑换雷吉斯奇鲁*5</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="G799" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
@@ -30970,7 +30970,7 @@
       </c>
       <c r="G800" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="G801" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="G802" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="G803" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -31138,7 +31138,7 @@
       </c>
       <c r="G804" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="G805" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="G806" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="G807" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="G808" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="G809" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -31380,7 +31380,7 @@
       </c>
       <c r="G810" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -31417,7 +31417,7 @@
       </c>
       <c r="G811" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -31454,7 +31454,7 @@
       </c>
       <c r="G812" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -31491,7 +31491,7 @@
       </c>
       <c r="G813" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -31528,7 +31528,7 @@
       </c>
       <c r="G814" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G815" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="G816" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G817" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G819" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
@@ -31721,7 +31721,7 @@
       </c>
       <c r="G820" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
@@ -31763,7 +31763,7 @@
       </c>
       <c r="G821" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="G822" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
@@ -31847,7 +31847,7 @@
       </c>
       <c r="G823" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="G825" s="4" t="inlineStr">
         <is>
-          <t>ハロウィンアイコン*1</t>
+          <t>万圣节图标*1</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="G826" s="4" t="inlineStr">
         <is>
-          <t>ハロウィンフレーム*1</t>
+          <t>万圣节框架*1</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
@@ -31976,7 +31976,7 @@
       </c>
       <c r="G827" s="4" t="inlineStr">
         <is>
-          <t>ハロウィン称号*1</t>
+          <t>万圣节称号*1</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="G828" s="4" t="inlineStr">
         <is>
-          <t>ハロウィン金貨パック*1</t>
+          <t>万圣节金币包*1</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="G829" s="4" t="inlineStr">
         <is>
-          <t>ハロウィン金貨パック*1</t>
+          <t>万圣节金币包*1</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
@@ -32102,7 +32102,7 @@
       </c>
       <c r="G830" s="4" t="inlineStr">
         <is>
-          <t>スパイ万能欠片*1</t>
+          <t>间谍万能碎片*1</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="G831" s="5" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム</t>
+          <t>装饰星星项目</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="G832" s="1" t="inlineStr">
         <is>
-          <t>銀の首飾り*1</t>
+          <t>银项链*1</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
@@ -32228,7 +32228,7 @@
       </c>
       <c r="G833" s="1" t="inlineStr">
         <is>
-          <t>紫·強化*1</t>
+          <t>紫色强化*1</t>
         </is>
       </c>
       <c r="H833" t="inlineStr">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="G837" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -32438,7 +32438,7 @@
       </c>
       <c r="G838" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -32483,7 +32483,7 @@
       </c>
       <c r="G840" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -32520,7 +32520,7 @@
       </c>
       <c r="G841" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -32557,7 +32557,7 @@
       </c>
       <c r="G842" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="G843" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -32631,7 +32631,7 @@
       </c>
       <c r="G844" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷吉斯奇鲁*5</t>
+          <t>紫色优惠券*6兑换雷吉斯奇鲁*5</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
@@ -32673,7 +32673,7 @@
       </c>
       <c r="G845" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H845" t="inlineStr">
@@ -32715,7 +32715,7 @@
       </c>
       <c r="G846" s="4" t="inlineStr">
         <is>
-          <t>紫クーポン*6   交換   雷公のカケラ*5</t>
+          <t>紫色优惠券*6交换雷公碎片*5</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="G847" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   烛光灵のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换烛光灵片*3</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -32799,7 +32799,7 @@
       </c>
       <c r="G848" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -32841,7 +32841,7 @@
       </c>
       <c r="G849" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3   交換   单首龙のカケラ*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3交换单首龙碎片*3</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="G850" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   {0}のカケラ*3</t>
+          <t>蓝色优惠券*5交换{0}碎片*3</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
@@ -32925,7 +32925,7 @@
       </c>
       <c r="G851" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   火狐狸のカケラ*3</t>
+          <t>蓝色优惠券*5交换火狐狸的碎片*3</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -32967,7 +32967,7 @@
       </c>
       <c r="G852" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   咕妞妞のカケラ*3</t>
+          <t>蓝色优惠券*5交换咕妞晴朗的碎片*3</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G853" s="4" t="inlineStr">
         <is>
-          <t>青クーポン*5   交換   海星星のカケラ*3</t>
+          <t>蓝色优惠券*5兑换海星星星碎片*3</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -33051,7 +33051,7 @@
       </c>
       <c r="G854" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -33088,7 +33088,7 @@
       </c>
       <c r="G855" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -33125,7 +33125,7 @@
       </c>
       <c r="G856" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="G857" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G858" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="G859" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G860" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="G861" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -33347,7 +33347,7 @@
       </c>
       <c r="G862" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="G863" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="G865" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -33466,7 +33466,7 @@
       </c>
       <c r="G866" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
@@ -33508,7 +33508,7 @@
       </c>
       <c r="G867" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="G868" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -33592,7 +33592,7 @@
       </c>
       <c r="G869" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -33637,7 +33637,7 @@
       </c>
       <c r="G871" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
@@ -33674,7 +33674,7 @@
       </c>
       <c r="G872" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="G873" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="G874" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="G875" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -33827,7 +33827,7 @@
       </c>
       <c r="G876" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H876" t="inlineStr">
@@ -33869,7 +33869,7 @@
       </c>
       <c r="G877" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
@@ -33911,7 +33911,7 @@
       </c>
       <c r="G878" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
@@ -33953,7 +33953,7 @@
       </c>
       <c r="G879" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G880" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -34037,7 +34037,7 @@
       </c>
       <c r="G881" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
@@ -34079,7 +34079,7 @@
       </c>
       <c r="G882" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
@@ -34121,7 +34121,7 @@
       </c>
       <c r="G883" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="G884" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
@@ -34205,7 +34205,7 @@
       </c>
       <c r="G885" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -34247,7 +34247,7 @@
       </c>
       <c r="G886" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="G887" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
@@ -34331,7 +34331,7 @@
       </c>
       <c r="G888" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="H888" t="inlineStr">
@@ -34373,7 +34373,7 @@
       </c>
       <c r="G889" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="H889" t="inlineStr">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G890" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
@@ -34457,7 +34457,7 @@
       </c>
       <c r="G891" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="G892" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="G893" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
@@ -34583,7 +34583,7 @@
       </c>
       <c r="G894" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
@@ -34628,7 +34628,7 @@
       </c>
       <c r="G896" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
@@ -34670,7 +34670,7 @@
       </c>
       <c r="G897" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
@@ -34712,7 +34712,7 @@
       </c>
       <c r="G898" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -34754,7 +34754,7 @@
       </c>
       <c r="G899" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
@@ -34796,7 +34796,7 @@
       </c>
       <c r="G900" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -34841,7 +34841,7 @@
       </c>
       <c r="G902" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -34878,7 +34878,7 @@
       </c>
       <c r="G903" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -34915,7 +34915,7 @@
       </c>
       <c r="G904" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -34952,7 +34952,7 @@
       </c>
       <c r="G905" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -34989,7 +34989,7 @@
       </c>
       <c r="G906" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="G907" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
@@ -35073,7 +35073,7 @@
       </c>
       <c r="G908" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
@@ -35115,7 +35115,7 @@
       </c>
       <c r="G909" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
@@ -35157,7 +35157,7 @@
       </c>
       <c r="G910" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H910" t="inlineStr">
@@ -35199,7 +35199,7 @@
       </c>
       <c r="G911" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="G912" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
@@ -35283,7 +35283,7 @@
       </c>
       <c r="G913" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G914" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
@@ -35367,7 +35367,7 @@
       </c>
       <c r="G915" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H915" t="inlineStr">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="G916" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -35446,7 +35446,7 @@
       </c>
       <c r="G917" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -35483,7 +35483,7 @@
       </c>
       <c r="G918" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -35520,7 +35520,7 @@
       </c>
       <c r="G919" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
@@ -35557,7 +35557,7 @@
       </c>
       <c r="G920" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -35594,7 +35594,7 @@
       </c>
       <c r="G921" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G922" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -35668,7 +35668,7 @@
       </c>
       <c r="G923" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G924" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -35742,7 +35742,7 @@
       </c>
       <c r="G925" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -35782,7 +35782,7 @@
       </c>
       <c r="G927" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
@@ -35824,7 +35824,7 @@
       </c>
       <c r="G928" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
@@ -35866,7 +35866,7 @@
       </c>
       <c r="G929" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
@@ -35908,7 +35908,7 @@
       </c>
       <c r="G930" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="G931" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
@@ -35995,7 +35995,7 @@
       </c>
       <c r="G933" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -36037,7 +36037,7 @@
       </c>
       <c r="G934" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -36079,7 +36079,7 @@
       </c>
       <c r="G935" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -36121,7 +36121,7 @@
       </c>
       <c r="G936" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G937" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
@@ -36245,7 +36245,7 @@
       </c>
       <c r="G940" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
@@ -36282,7 +36282,7 @@
       </c>
       <c r="G941" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
@@ -36319,7 +36319,7 @@
       </c>
       <c r="G942" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="G943" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="G944" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
@@ -36435,7 +36435,7 @@
       </c>
       <c r="G945" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="G946" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="G947" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
@@ -36561,7 +36561,7 @@
       </c>
       <c r="G948" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
@@ -36603,7 +36603,7 @@
       </c>
       <c r="G949" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
@@ -36645,7 +36645,7 @@
       </c>
       <c r="G950" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
@@ -36687,7 +36687,7 @@
       </c>
       <c r="G951" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
@@ -36729,7 +36729,7 @@
       </c>
       <c r="G952" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G953" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="G954" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
@@ -36850,7 +36850,7 @@
       </c>
       <c r="G955" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
@@ -36887,7 +36887,7 @@
       </c>
       <c r="G956" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
@@ -36924,7 +36924,7 @@
       </c>
       <c r="G957" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G958" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="G959" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="G960" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
@@ -37072,7 +37072,7 @@
       </c>
       <c r="G961" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
@@ -37109,7 +37109,7 @@
       </c>
       <c r="G962" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
@@ -37146,7 +37146,7 @@
       </c>
       <c r="G963" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="G967" s="1" t="inlineStr">
         <is>
-          <t>団子フレーム</t>
+          <t>团子框架</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
@@ -37312,7 +37312,7 @@
       </c>
       <c r="G968" s="1" t="inlineStr">
         <is>
-          <t>円満</t>
+          <t>圆满</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
@@ -37438,7 +37438,7 @@
       </c>
       <c r="G971" s="1" t="inlineStr">
         <is>
-          <t>天賦Pt*2</t>
+          <t>天赋Pt*2</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
@@ -37522,7 +37522,7 @@
       </c>
       <c r="G973" s="5" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム*1</t>
+          <t>装饰星星物品*1</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
@@ -37564,7 +37564,7 @@
       </c>
       <c r="G974" s="1" t="inlineStr">
         <is>
-          <t>ガチャ券*1</t>
+          <t>扭蛋券*1</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -37606,7 +37606,7 @@
       </c>
       <c r="G975" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャ*2</t>
+          <t>装饰扭蛋*2</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
@@ -37648,7 +37648,7 @@
       </c>
       <c r="G976" s="5" t="inlineStr">
         <is>
-          <t>探査機ガチャ券*1</t>
+          <t>探测器游戏券*1</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
@@ -37690,7 +37690,7 @@
       </c>
       <c r="G977" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
@@ -37774,7 +37774,7 @@
       </c>
       <c r="G979" s="1" t="inlineStr">
         <is>
-          <t>青強化*1</t>
+          <t>蓝色强化*1</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
@@ -37816,7 +37816,7 @@
       </c>
       <c r="G980" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
@@ -37858,7 +37858,7 @@
       </c>
       <c r="G981" s="1" t="inlineStr">
         <is>
-          <t>高級好感度ギフト*1</t>
+          <t>高级好感度礼品*1</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
@@ -37945,7 +37945,7 @@
       </c>
       <c r="G984" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -37982,7 +37982,7 @@
       </c>
       <c r="G985" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="G986" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="G987" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="G988" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H988" t="inlineStr">
@@ -38135,7 +38135,7 @@
       </c>
       <c r="G989" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G990" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H990" t="inlineStr">
@@ -38219,7 +38219,7 @@
       </c>
       <c r="G991" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
@@ -38261,7 +38261,7 @@
       </c>
       <c r="G992" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H992" t="inlineStr">
@@ -38303,7 +38303,7 @@
       </c>
       <c r="G993" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
@@ -38345,7 +38345,7 @@
       </c>
       <c r="G994" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H994" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="G995" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="G996" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H996" t="inlineStr">
@@ -38471,7 +38471,7 @@
       </c>
       <c r="G997" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="G998" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="G999" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -38587,7 +38587,7 @@
       </c>
       <c r="G1000" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -38624,7 +38624,7 @@
       </c>
       <c r="G1001" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="G1002" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -38698,7 +38698,7 @@
       </c>
       <c r="G1003" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="G1004" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -38772,7 +38772,7 @@
       </c>
       <c r="G1005" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -38809,7 +38809,7 @@
       </c>
       <c r="G1006" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="G1007" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="G1009" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1009" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="G1010" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr">
@@ -38970,7 +38970,7 @@
       </c>
       <c r="G1011" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="G1012" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="G1013" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1013" t="inlineStr">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="G1015" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -39136,7 +39136,7 @@
       </c>
       <c r="G1016" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="G1017" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
@@ -39210,7 +39210,7 @@
       </c>
       <c r="G1018" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
@@ -39247,7 +39247,7 @@
       </c>
       <c r="G1019" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr">
@@ -39289,7 +39289,7 @@
       </c>
       <c r="G1020" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
@@ -39331,7 +39331,7 @@
       </c>
       <c r="G1021" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
@@ -39373,7 +39373,7 @@
       </c>
       <c r="G1022" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -39415,7 +39415,7 @@
       </c>
       <c r="G1023" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
@@ -39457,7 +39457,7 @@
       </c>
       <c r="G1024" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
@@ -39499,7 +39499,7 @@
       </c>
       <c r="G1025" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="G1026" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1026" t="inlineStr">
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G1027" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
@@ -39625,7 +39625,7 @@
       </c>
       <c r="G1028" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
@@ -39667,7 +39667,7 @@
       </c>
       <c r="G1029" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
@@ -39704,7 +39704,7 @@
       </c>
       <c r="G1030" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
@@ -39741,7 +39741,7 @@
       </c>
       <c r="G1031" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
@@ -39778,7 +39778,7 @@
       </c>
       <c r="G1032" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
@@ -39815,7 +39815,7 @@
       </c>
       <c r="G1033" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
@@ -39852,7 +39852,7 @@
       </c>
       <c r="G1034" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
@@ -39889,7 +39889,7 @@
       </c>
       <c r="G1035" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
@@ -39926,7 +39926,7 @@
       </c>
       <c r="G1036" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1036" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G1037" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="G1038" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
@@ -40040,7 +40040,7 @@
       </c>
       <c r="G1040" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1040" t="inlineStr">
@@ -40082,7 +40082,7 @@
       </c>
       <c r="G1041" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
@@ -40124,7 +40124,7 @@
       </c>
       <c r="G1042" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr">
@@ -40166,7 +40166,7 @@
       </c>
       <c r="G1043" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="G1044" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1044" t="inlineStr">
@@ -40253,7 +40253,7 @@
       </c>
       <c r="G1046" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1046" t="inlineStr">
@@ -40290,7 +40290,7 @@
       </c>
       <c r="G1047" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1047" t="inlineStr">
@@ -40327,7 +40327,7 @@
       </c>
       <c r="G1048" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1048" t="inlineStr">
@@ -40364,7 +40364,7 @@
       </c>
       <c r="G1049" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
@@ -40401,7 +40401,7 @@
       </c>
       <c r="G1050" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1050" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="G1051" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
@@ -40485,7 +40485,7 @@
       </c>
       <c r="G1052" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1052" t="inlineStr">
@@ -40527,7 +40527,7 @@
       </c>
       <c r="G1053" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="G1054" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1054" t="inlineStr">
@@ -40611,7 +40611,7 @@
       </c>
       <c r="G1055" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
@@ -40653,7 +40653,7 @@
       </c>
       <c r="G1056" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="G1057" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
@@ -40737,7 +40737,7 @@
       </c>
       <c r="G1058" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
@@ -40779,7 +40779,7 @@
       </c>
       <c r="G1059" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1059" t="inlineStr">
@@ -40821,7 +40821,7 @@
       </c>
       <c r="G1060" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
@@ -40858,7 +40858,7 @@
       </c>
       <c r="G1061" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
@@ -40895,7 +40895,7 @@
       </c>
       <c r="G1062" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
@@ -40932,7 +40932,7 @@
       </c>
       <c r="G1063" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
@@ -40969,7 +40969,7 @@
       </c>
       <c r="G1064" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="G1065" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
@@ -41043,7 +41043,7 @@
       </c>
       <c r="G1066" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
@@ -41080,7 +41080,7 @@
       </c>
       <c r="G1067" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1067" t="inlineStr">
@@ -41117,7 +41117,7 @@
       </c>
       <c r="G1068" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="G1069" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
@@ -41194,7 +41194,7 @@
       </c>
       <c r="G1071" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1071" t="inlineStr">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="G1072" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
@@ -41278,7 +41278,7 @@
       </c>
       <c r="G1073" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1073" t="inlineStr">
@@ -41320,7 +41320,7 @@
       </c>
       <c r="G1074" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr">
@@ -41362,7 +41362,7 @@
       </c>
       <c r="G1075" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1075" t="inlineStr">
@@ -41407,7 +41407,7 @@
       </c>
       <c r="G1077" s="1" t="inlineStr">
         <is>
-          <t>こどもの日フレーム*1</t>
+          <t>儿童节框架*1</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr">
@@ -41449,7 +41449,7 @@
       </c>
       <c r="G1078" s="1" t="inlineStr">
         <is>
-          <t>こどもの日パック</t>
+          <t>儿童节包</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr">
@@ -41491,7 +41491,7 @@
       </c>
       <c r="G1079" s="1" t="inlineStr">
         <is>
-          <t>こどもの日称号*1</t>
+          <t>儿童节称号*1</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr">
@@ -41533,7 +41533,7 @@
       </c>
       <c r="G1080" s="1" t="inlineStr">
         <is>
-          <t>こどもの日アイコン*1</t>
+          <t>儿童节图标*1</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr">
@@ -41575,7 +41575,7 @@
       </c>
       <c r="G1081" s="1" t="inlineStr">
         <is>
-          <t>こどもの日アイコン2*1</t>
+          <t>儿童节图标2*1</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr">
@@ -41617,7 +41617,7 @@
       </c>
       <c r="G1082" s="1" t="inlineStr">
         <is>
-          <t>こどもの日アイコン2*1</t>
+          <t>儿童节图标2*1</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr">
@@ -41659,7 +41659,7 @@
       </c>
       <c r="G1083" s="1" t="inlineStr">
         <is>
-          <t>こどもの日アイコン2*1</t>
+          <t>儿童节图标2*1</t>
         </is>
       </c>
       <c r="H1083" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="G1086" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr">
@@ -41827,7 +41827,7 @@
       </c>
       <c r="G1087" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H1087" t="inlineStr">
@@ -41872,7 +41872,7 @@
       </c>
       <c r="G1089" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
@@ -41909,7 +41909,7 @@
       </c>
       <c r="G1090" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1090" t="inlineStr">
@@ -41946,7 +41946,7 @@
       </c>
       <c r="G1091" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
@@ -41983,7 +41983,7 @@
       </c>
       <c r="G1092" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1092" t="inlineStr">
@@ -42020,7 +42020,7 @@
       </c>
       <c r="G1093" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1093" t="inlineStr">
@@ -42062,7 +42062,7 @@
       </c>
       <c r="G1094" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="G1095" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr">
@@ -42146,7 +42146,7 @@
       </c>
       <c r="G1096" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1096" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="G1097" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="G1098" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1098" t="inlineStr">
@@ -42272,7 +42272,7 @@
       </c>
       <c r="G1099" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1099" t="inlineStr">
@@ -42314,7 +42314,7 @@
       </c>
       <c r="G1100" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1100" t="inlineStr">
@@ -42356,7 +42356,7 @@
       </c>
       <c r="G1101" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1101" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="G1102" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1102" t="inlineStr">
@@ -42440,7 +42440,7 @@
       </c>
       <c r="G1103" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1103" t="inlineStr">
@@ -42477,7 +42477,7 @@
       </c>
       <c r="G1104" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1104" t="inlineStr">
@@ -42514,7 +42514,7 @@
       </c>
       <c r="G1105" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1105" t="inlineStr">
@@ -42551,7 +42551,7 @@
       </c>
       <c r="G1106" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1106" t="inlineStr">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="G1107" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1107" t="inlineStr">
@@ -42625,7 +42625,7 @@
       </c>
       <c r="G1108" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1108" t="inlineStr">
@@ -42662,7 +42662,7 @@
       </c>
       <c r="G1109" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1109" t="inlineStr">
@@ -42699,7 +42699,7 @@
       </c>
       <c r="G1110" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1110" t="inlineStr">
@@ -42736,7 +42736,7 @@
       </c>
       <c r="G1111" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1111" t="inlineStr">
@@ -42773,7 +42773,7 @@
       </c>
       <c r="G1112" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1112" t="inlineStr">
@@ -42813,7 +42813,7 @@
       </c>
       <c r="G1114" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1114" t="inlineStr">
@@ -42855,7 +42855,7 @@
       </c>
       <c r="G1115" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1115" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="G1116" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1116" t="inlineStr">
@@ -42939,7 +42939,7 @@
       </c>
       <c r="G1117" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1117" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="G1118" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1118" t="inlineStr">
@@ -43026,7 +43026,7 @@
       </c>
       <c r="G1120" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1120" t="inlineStr">
@@ -43063,7 +43063,7 @@
       </c>
       <c r="G1121" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1121" t="inlineStr">
@@ -43100,7 +43100,7 @@
       </c>
       <c r="G1122" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1122" t="inlineStr">
@@ -43137,7 +43137,7 @@
       </c>
       <c r="G1123" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1123" t="inlineStr">
@@ -43174,7 +43174,7 @@
       </c>
       <c r="G1124" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1124" t="inlineStr">
@@ -43216,7 +43216,7 @@
       </c>
       <c r="G1125" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1125" t="inlineStr">
@@ -43258,7 +43258,7 @@
       </c>
       <c r="G1126" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1126" t="inlineStr">
@@ -43300,7 +43300,7 @@
       </c>
       <c r="G1127" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1127" t="inlineStr">
@@ -43342,7 +43342,7 @@
       </c>
       <c r="G1128" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1128" t="inlineStr">
@@ -43384,7 +43384,7 @@
       </c>
       <c r="G1129" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1129" t="inlineStr">
@@ -43426,7 +43426,7 @@
       </c>
       <c r="G1130" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1130" t="inlineStr">
@@ -43468,7 +43468,7 @@
       </c>
       <c r="G1131" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1131" t="inlineStr">
@@ -43510,7 +43510,7 @@
       </c>
       <c r="G1132" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1132" t="inlineStr">
@@ -43552,7 +43552,7 @@
       </c>
       <c r="G1133" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1133" t="inlineStr">
@@ -43594,7 +43594,7 @@
       </c>
       <c r="G1134" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1134" t="inlineStr">
@@ -43631,7 +43631,7 @@
       </c>
       <c r="G1135" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1135" t="inlineStr">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="G1136" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1136" t="inlineStr">
@@ -43705,7 +43705,7 @@
       </c>
       <c r="G1137" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1137" t="inlineStr">
@@ -43742,7 +43742,7 @@
       </c>
       <c r="G1138" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1138" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="G1139" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1139" t="inlineStr">
@@ -43816,7 +43816,7 @@
       </c>
       <c r="G1140" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1140" t="inlineStr">
@@ -43853,7 +43853,7 @@
       </c>
       <c r="G1141" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1141" t="inlineStr">
@@ -43890,7 +43890,7 @@
       </c>
       <c r="G1142" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1142" t="inlineStr">
@@ -43927,7 +43927,7 @@
       </c>
       <c r="G1143" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1143" t="inlineStr">
@@ -43967,7 +43967,7 @@
       </c>
       <c r="G1145" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1145" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="G1146" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1146" t="inlineStr">
@@ -44051,7 +44051,7 @@
       </c>
       <c r="G1147" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1147" t="inlineStr">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="G1148" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1148" t="inlineStr">
@@ -44135,7 +44135,7 @@
       </c>
       <c r="G1149" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1149" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="G1151" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1151" t="inlineStr">
@@ -44217,7 +44217,7 @@
       </c>
       <c r="G1152" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1152" t="inlineStr">
@@ -44254,7 +44254,7 @@
       </c>
       <c r="G1153" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1153" t="inlineStr">
@@ -44291,7 +44291,7 @@
       </c>
       <c r="G1154" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
@@ -44328,7 +44328,7 @@
       </c>
       <c r="G1155" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1155" t="inlineStr">
@@ -44370,7 +44370,7 @@
       </c>
       <c r="G1156" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1156" t="inlineStr">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="G1157" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1157" t="inlineStr">
@@ -44454,7 +44454,7 @@
       </c>
       <c r="G1158" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1158" t="inlineStr">
@@ -44496,7 +44496,7 @@
       </c>
       <c r="G1159" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1159" t="inlineStr">
@@ -44538,7 +44538,7 @@
       </c>
       <c r="G1160" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1160" t="inlineStr">
@@ -44580,7 +44580,7 @@
       </c>
       <c r="G1161" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1161" t="inlineStr">
@@ -44622,7 +44622,7 @@
       </c>
       <c r="G1162" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1162" t="inlineStr">
@@ -44664,7 +44664,7 @@
       </c>
       <c r="G1163" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1163" t="inlineStr">
@@ -44706,7 +44706,7 @@
       </c>
       <c r="G1164" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1164" t="inlineStr">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="G1165" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1165" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="G1166" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1166" t="inlineStr">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="G1167" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1167" t="inlineStr">
@@ -44859,7 +44859,7 @@
       </c>
       <c r="G1168" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1168" t="inlineStr">
@@ -44896,7 +44896,7 @@
       </c>
       <c r="G1169" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1169" t="inlineStr">
@@ -44933,7 +44933,7 @@
       </c>
       <c r="G1170" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1170" t="inlineStr">
@@ -44970,7 +44970,7 @@
       </c>
       <c r="G1171" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1171" t="inlineStr">
@@ -45007,7 +45007,7 @@
       </c>
       <c r="G1172" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1172" t="inlineStr">
@@ -45044,7 +45044,7 @@
       </c>
       <c r="G1173" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1173" t="inlineStr">
@@ -45081,7 +45081,7 @@
       </c>
       <c r="G1174" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1174" t="inlineStr">
@@ -45121,7 +45121,7 @@
       </c>
       <c r="G1176" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1176" t="inlineStr">
@@ -45163,7 +45163,7 @@
       </c>
       <c r="G1177" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1177" t="inlineStr">
@@ -45205,7 +45205,7 @@
       </c>
       <c r="G1178" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1178" t="inlineStr">
@@ -45247,7 +45247,7 @@
       </c>
       <c r="G1179" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1179" t="inlineStr">
@@ -45289,7 +45289,7 @@
       </c>
       <c r="G1180" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1180" t="inlineStr">
@@ -45334,7 +45334,7 @@
       </c>
       <c r="G1182" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1182" t="inlineStr">
@@ -45371,7 +45371,7 @@
       </c>
       <c r="G1183" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1183" t="inlineStr">
@@ -45408,7 +45408,7 @@
       </c>
       <c r="G1184" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1184" t="inlineStr">
@@ -45445,7 +45445,7 @@
       </c>
       <c r="G1185" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1185" t="inlineStr">
@@ -45482,7 +45482,7 @@
       </c>
       <c r="G1186" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1186" t="inlineStr">
@@ -45524,7 +45524,7 @@
       </c>
       <c r="G1187" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1187" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="G1188" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1188" t="inlineStr">
@@ -45608,7 +45608,7 @@
       </c>
       <c r="G1189" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1189" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="G1190" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1190" t="inlineStr">
@@ -45692,7 +45692,7 @@
       </c>
       <c r="G1191" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1191" t="inlineStr">
@@ -45734,7 +45734,7 @@
       </c>
       <c r="G1192" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1192" t="inlineStr">
@@ -45776,7 +45776,7 @@
       </c>
       <c r="G1193" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1193" t="inlineStr">
@@ -45818,7 +45818,7 @@
       </c>
       <c r="G1194" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1194" t="inlineStr">
@@ -45860,7 +45860,7 @@
       </c>
       <c r="G1195" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1195" t="inlineStr">
@@ -45902,7 +45902,7 @@
       </c>
       <c r="G1196" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1196" t="inlineStr">
@@ -45939,7 +45939,7 @@
       </c>
       <c r="G1197" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1197" t="inlineStr">
@@ -45976,7 +45976,7 @@
       </c>
       <c r="G1198" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1198" t="inlineStr">
@@ -46013,7 +46013,7 @@
       </c>
       <c r="G1199" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1199" t="inlineStr">
@@ -46050,7 +46050,7 @@
       </c>
       <c r="G1200" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1200" t="inlineStr">
@@ -46087,7 +46087,7 @@
       </c>
       <c r="G1201" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1201" t="inlineStr">
@@ -46124,7 +46124,7 @@
       </c>
       <c r="G1202" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1202" t="inlineStr">
@@ -46161,7 +46161,7 @@
       </c>
       <c r="G1203" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1203" t="inlineStr">
@@ -46198,7 +46198,7 @@
       </c>
       <c r="G1204" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1204" t="inlineStr">
@@ -46235,7 +46235,7 @@
       </c>
       <c r="G1205" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1205" t="inlineStr">
@@ -46275,7 +46275,7 @@
       </c>
       <c r="G1207" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1207" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="G1208" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1208" t="inlineStr">
@@ -46359,7 +46359,7 @@
       </c>
       <c r="G1209" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1209" t="inlineStr">
@@ -46401,7 +46401,7 @@
       </c>
       <c r="G1210" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1210" t="inlineStr">
@@ -46443,7 +46443,7 @@
       </c>
       <c r="G1211" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1211" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="G1213" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1213" t="inlineStr">
@@ -46525,7 +46525,7 @@
       </c>
       <c r="G1214" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1214" t="inlineStr">
@@ -46562,7 +46562,7 @@
       </c>
       <c r="G1215" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1215" t="inlineStr">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="G1216" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1216" t="inlineStr">
@@ -46636,7 +46636,7 @@
       </c>
       <c r="G1217" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1217" t="inlineStr">
@@ -46678,7 +46678,7 @@
       </c>
       <c r="G1218" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1218" t="inlineStr">
@@ -46720,7 +46720,7 @@
       </c>
       <c r="G1219" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1219" t="inlineStr">
@@ -46762,7 +46762,7 @@
       </c>
       <c r="G1220" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1220" t="inlineStr">
@@ -46804,7 +46804,7 @@
       </c>
       <c r="G1221" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1221" t="inlineStr">
@@ -46846,7 +46846,7 @@
       </c>
       <c r="G1222" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1222" t="inlineStr">
@@ -46888,7 +46888,7 @@
       </c>
       <c r="G1223" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1223" t="inlineStr">
@@ -46930,7 +46930,7 @@
       </c>
       <c r="G1224" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1224" t="inlineStr">
@@ -46972,7 +46972,7 @@
       </c>
       <c r="G1225" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1225" t="inlineStr">
@@ -47014,7 +47014,7 @@
       </c>
       <c r="G1226" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1226" t="inlineStr">
@@ -47056,7 +47056,7 @@
       </c>
       <c r="G1227" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1227" t="inlineStr">
@@ -47093,7 +47093,7 @@
       </c>
       <c r="G1228" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1228" t="inlineStr">
@@ -47130,7 +47130,7 @@
       </c>
       <c r="G1229" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1229" t="inlineStr">
@@ -47167,7 +47167,7 @@
       </c>
       <c r="G1230" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1230" t="inlineStr">
@@ -47204,7 +47204,7 @@
       </c>
       <c r="G1231" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1231" t="inlineStr">
@@ -47241,7 +47241,7 @@
       </c>
       <c r="G1232" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1232" t="inlineStr">
@@ -47278,7 +47278,7 @@
       </c>
       <c r="G1233" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1233" t="inlineStr">
@@ -47315,7 +47315,7 @@
       </c>
       <c r="G1234" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1234" t="inlineStr">
@@ -47352,7 +47352,7 @@
       </c>
       <c r="G1235" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1235" t="inlineStr">
@@ -47389,7 +47389,7 @@
       </c>
       <c r="G1236" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1236" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="G1238" s="1" t="inlineStr">
         <is>
-          <t>紅葉アイコン</t>
+          <t>红叶图标</t>
         </is>
       </c>
       <c r="I1238" t="inlineStr">
@@ -47466,7 +47466,7 @@
       </c>
       <c r="G1239" s="1" t="inlineStr">
         <is>
-          <t>紅葉称号</t>
+          <t>红叶称号</t>
         </is>
       </c>
       <c r="I1239" t="inlineStr">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="G1240" s="1" t="inlineStr">
         <is>
-          <t>紅葉アイコン</t>
+          <t>红叶图标</t>
         </is>
       </c>
       <c r="I1240" t="inlineStr">
@@ -47614,7 +47614,7 @@
       </c>
       <c r="G1243" s="1" t="inlineStr">
         <is>
-          <t>S仲間選択宝箱</t>
+          <t>S伙伴选择宝箱</t>
         </is>
       </c>
       <c r="I1243" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="G1244" s="1" t="inlineStr">
         <is>
-          <t>装飾覚醒選択宝箱</t>
+          <t>装饰觉醒选择宝箱</t>
         </is>
       </c>
       <c r="I1244" t="inlineStr">
@@ -47725,7 +47725,7 @@
       </c>
       <c r="G1246" s="1" t="inlineStr">
         <is>
-          <t>ダイヤ</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="I1246" t="inlineStr">
@@ -47762,7 +47762,7 @@
       </c>
       <c r="G1247" s="1" t="inlineStr">
         <is>
-          <t>ランダム橙·ルーン宝箱</t>
+          <t>随机橙符文宝箱</t>
         </is>
       </c>
       <c r="I1247" t="inlineStr">
@@ -47799,7 +47799,7 @@
       </c>
       <c r="G1248" s="5" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム</t>
+          <t>装饰星星项目</t>
         </is>
       </c>
       <c r="I1248" t="inlineStr">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="G1249" s="5" t="inlineStr">
         <is>
-          <t>紫·探査機宝箱</t>
+          <t>紫色探测器宝箱</t>
         </is>
       </c>
       <c r="I1249" t="inlineStr">
@@ -47873,7 +47873,7 @@
       </c>
       <c r="G1250" s="1" t="inlineStr">
         <is>
-          <t>天賦Pt</t>
+          <t>天赋Pt</t>
         </is>
       </c>
       <c r="I1250" t="inlineStr">
@@ -47910,7 +47910,7 @@
       </c>
       <c r="G1251" s="1" t="inlineStr">
         <is>
-          <t>ランダム橙·ルーン宝箱</t>
+          <t>随机橙符文宝箱</t>
         </is>
       </c>
       <c r="I1251" t="inlineStr">
@@ -47947,7 +47947,7 @@
       </c>
       <c r="G1252" s="1" t="inlineStr">
         <is>
-          <t>金貨</t>
+          <t>金币</t>
         </is>
       </c>
       <c r="I1252" t="inlineStr">
@@ -48021,7 +48021,7 @@
       </c>
       <c r="G1254" s="1" t="inlineStr">
         <is>
-          <t>強化薬</t>
+          <t>强化药</t>
         </is>
       </c>
       <c r="I1254" t="inlineStr">
@@ -48058,7 +48058,7 @@
       </c>
       <c r="G1255" s="1" t="inlineStr">
         <is>
-          <t>紫·装備強化アイテム</t>
+          <t>紫色装备强化道具</t>
         </is>
       </c>
       <c r="I1255" t="inlineStr">
@@ -48098,7 +48098,7 @@
       </c>
       <c r="G1257" s="1" t="inlineStr">
         <is>
-          <t>紫·装備万能*1</t>
+          <t>紫色装备万能*1</t>
         </is>
       </c>
       <c r="H1257" t="inlineStr">
@@ -48140,7 +48140,7 @@
       </c>
       <c r="G1258" s="1" t="inlineStr">
         <is>
-          <t>紫·装備セレクト*1</t>
+          <t>紫色装备选择*1</t>
         </is>
       </c>
       <c r="H1258" t="inlineStr">
@@ -48182,7 +48182,7 @@
       </c>
       <c r="G1259" s="1" t="inlineStr">
         <is>
-          <t>橙·装備万能*1</t>
+          <t>橙色装备万能*1</t>
         </is>
       </c>
       <c r="H1259" t="inlineStr">
@@ -48224,7 +48224,7 @@
       </c>
       <c r="G1260" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1260" t="inlineStr">
@@ -48266,7 +48266,7 @@
       </c>
       <c r="G1261" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1261" t="inlineStr">
@@ -48308,7 +48308,7 @@
       </c>
       <c r="G1262" s="1" t="inlineStr">
         <is>
-          <t>橙·装備*1</t>
+          <t>橙色装备*1</t>
         </is>
       </c>
       <c r="H1262" t="inlineStr">
@@ -48353,7 +48353,7 @@
       </c>
       <c r="G1264" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   普通万能のカケラ*1</t>
+          <t>蓝色优惠券*2交换普通万能的碎片*1</t>
         </is>
       </c>
       <c r="I1264" t="inlineStr">
@@ -48390,7 +48390,7 @@
       </c>
       <c r="G1265" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   普通万能のカケラ*2</t>
+          <t>紫色优惠券*4交换普通万能片*2</t>
         </is>
       </c>
       <c r="I1265" t="inlineStr">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="G1266" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   天賦PT*1</t>
+          <t>蓝色优惠券*2交换天赋PT*1</t>
         </is>
       </c>
       <c r="I1266" t="inlineStr">
@@ -48464,7 +48464,7 @@
       </c>
       <c r="G1267" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*4   交換   天賦PT*2</t>
+          <t>紫色优惠券*4交换天赋PT*2</t>
         </is>
       </c>
       <c r="I1267" t="inlineStr">
@@ -48501,7 +48501,7 @@
       </c>
       <c r="G1268" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1268" t="inlineStr">
@@ -48543,7 +48543,7 @@
       </c>
       <c r="G1269" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1269" t="inlineStr">
@@ -48585,7 +48585,7 @@
       </c>
       <c r="G1270" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*6</t>
+          <t>紫色优惠券*6</t>
         </is>
       </c>
       <c r="H1270" t="inlineStr">
@@ -48627,7 +48627,7 @@
       </c>
       <c r="G1271" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1271" t="inlineStr">
@@ -48669,7 +48669,7 @@
       </c>
       <c r="G1272" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1272" t="inlineStr">
@@ -48711,7 +48711,7 @@
       </c>
       <c r="G1273" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*3 紫クーポン*3</t>
+          <t>蓝色优惠券*3紫色优惠券*3</t>
         </is>
       </c>
       <c r="H1273" t="inlineStr">
@@ -48753,7 +48753,7 @@
       </c>
       <c r="G1274" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1274" t="inlineStr">
@@ -48795,7 +48795,7 @@
       </c>
       <c r="G1275" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1275" t="inlineStr">
@@ -48837,7 +48837,7 @@
       </c>
       <c r="G1276" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1276" t="inlineStr">
@@ -48879,7 +48879,7 @@
       </c>
       <c r="G1277" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*5</t>
+          <t>蓝色优惠券*5</t>
         </is>
       </c>
       <c r="H1277" t="inlineStr">
@@ -48921,7 +48921,7 @@
       </c>
       <c r="G1278" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   不思議なカプセル*1</t>
+          <t>蓝色优惠券*2交换神奇胶囊*1</t>
         </is>
       </c>
       <c r="I1278" t="inlineStr">
@@ -48958,7 +48958,7 @@
       </c>
       <c r="G1279" s="1" t="inlineStr">
         <is>
-          <t>紫クーポン*2   交換   不思議なカプセル*2</t>
+          <t>紫色优惠券*2交换神奇胶囊*2</t>
         </is>
       </c>
       <c r="I1279" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="G1280" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*8 紫クーポン*8   交換   金の鍵*10</t>
+          <t>蓝色优惠券*8紫色优惠券*8兑换金钥匙*10</t>
         </is>
       </c>
       <c r="I1280" t="inlineStr">
@@ -49032,7 +49032,7 @@
       </c>
       <c r="G1281" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   紫色携带强化*3</t>
+          <t>蓝色优惠券*6交换紫色手机增强*3</t>
         </is>
       </c>
       <c r="I1281" t="inlineStr">
@@ -49069,7 +49069,7 @@
       </c>
       <c r="G1282" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*6   交換   エネルギーの薬*30</t>
+          <t>蓝色优惠券*6交换能量药水*30</t>
         </is>
       </c>
       <c r="I1282" t="inlineStr">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="G1283" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2   交換   金貨*100000</t>
+          <t>蓝色优惠券*2兑换金币*100000</t>
         </is>
       </c>
       <c r="I1283" t="inlineStr">
@@ -49143,7 +49143,7 @@
       </c>
       <c r="G1284" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*2 紫クーポン*5   交換   质朴配饰*1</t>
+          <t>蓝色优惠券*2紫色优惠券*5兑换质朴饰品*1</t>
         </is>
       </c>
       <c r="I1284" t="inlineStr">
@@ -49180,7 +49180,7 @@
       </c>
       <c r="G1285" s="5" t="inlineStr">
         <is>
-          <t>青クーポン*30 紫クーポン*75   交換   紫装備道具箱*1</t>
+          <t>蓝色优惠券*30紫色优惠券*75更换紫色装备工具箱*1</t>
         </is>
       </c>
       <c r="I1285" t="inlineStr">
@@ -49217,7 +49217,7 @@
       </c>
       <c r="G1286" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   饰品觉醒选择箱子*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45更换饰品觉醒选择盒子*1</t>
         </is>
       </c>
       <c r="I1286" t="inlineStr">
@@ -49254,7 +49254,7 @@
       </c>
       <c r="G1287" s="1" t="inlineStr">
         <is>
-          <t>青クーポン*15 紫クーポン*45   交換   装飾覚醒ランダム箱*1</t>
+          <t>蓝色优惠券*15紫色优惠券*45交换装饰觉醒随机盒*1</t>
         </is>
       </c>
       <c r="I1287" t="inlineStr">
@@ -49294,7 +49294,7 @@
       </c>
       <c r="G1289" s="4" t="inlineStr">
         <is>
-          <t>中级Z觉醒のカケラ</t>
+          <t>中级Z觉醒的碎片</t>
         </is>
       </c>
       <c r="I1289" t="inlineStr">
@@ -49331,7 +49331,7 @@
       </c>
       <c r="G1290" s="4" t="inlineStr">
         <is>
-          <t>高级Z觉醒のカケラ</t>
+          <t>高级Z觉醒的碎片</t>
         </is>
       </c>
       <c r="I1290" t="inlineStr">
@@ -49368,7 +49368,7 @@
       </c>
       <c r="G1291" s="7" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム</t>
+          <t>装饰星星项目</t>
         </is>
       </c>
       <c r="I1291" t="inlineStr">
@@ -49405,7 +49405,7 @@
       </c>
       <c r="G1292" s="4" t="inlineStr">
         <is>
-          <t>スパイ万能欠片</t>
+          <t>间谍万能碎片</t>
         </is>
       </c>
       <c r="I1292" t="inlineStr">
@@ -49442,7 +49442,7 @@
       </c>
       <c r="G1293" s="4" t="inlineStr">
         <is>
-          <t>最も古い4つの橙·装備宝箱</t>
+          <t>最古老的四个橙装备宝箱</t>
         </is>
       </c>
       <c r="I1293" t="inlineStr">
@@ -49479,7 +49479,7 @@
       </c>
       <c r="G1294" s="4" t="inlineStr">
         <is>
-          <t>コア洗練</t>
+          <t>核心精炼</t>
         </is>
       </c>
       <c r="I1294" t="inlineStr">
@@ -49521,7 +49521,7 @@
       </c>
       <c r="G1295" s="4" t="inlineStr">
         <is>
-          <t>蒂安希のカケラ</t>
+          <t>蒂安希的作品</t>
         </is>
       </c>
       <c r="I1295" t="inlineStr">
@@ -49563,7 +49563,7 @@
       </c>
       <c r="G1296" s="4" t="inlineStr">
         <is>
-          <t>洛奇亚のカケラ</t>
+          <t>洛奇亚的碎片</t>
         </is>
       </c>
       <c r="I1296" t="inlineStr">
@@ -49605,7 +49605,7 @@
       </c>
       <c r="G1297" s="4" t="inlineStr">
         <is>
-          <t>盖欧卡のカケラ</t>
+          <t>盖欧卡的碎片</t>
         </is>
       </c>
       <c r="I1297" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="G1298" s="4" t="inlineStr">
         <is>
-          <t>达克莱伊のカケラ</t>
+          <t>达克莱伊的碎片</t>
         </is>
       </c>
       <c r="I1298" t="inlineStr">
@@ -49689,7 +49689,7 @@
       </c>
       <c r="G1299" s="4" t="inlineStr">
         <is>
-          <t>雷吉奇卡斯のカケラ</t>
+          <t>雷吉奇卡斯碎片</t>
         </is>
       </c>
       <c r="I1299" t="inlineStr">
@@ -49731,7 +49731,7 @@
       </c>
       <c r="G1300" s="4" t="inlineStr">
         <is>
-          <t>帝牙卢卡のカケラ</t>
+          <t>帝牙卢卡的碎片</t>
         </is>
       </c>
       <c r="I1300" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="G1301" s="4" t="inlineStr">
         <is>
-          <t>帕路奇亚のカケラ</t>
+          <t>帕路奇亚的碎片</t>
         </is>
       </c>
       <c r="I1301" t="inlineStr">
@@ -49815,7 +49815,7 @@
       </c>
       <c r="G1302" s="4" t="inlineStr">
         <is>
-          <t>藤琳杏のカケラ</t>
+          <t>藤琳杏的碎片</t>
         </is>
       </c>
       <c r="I1302" t="inlineStr">
@@ -49852,7 +49852,7 @@
       </c>
       <c r="G1303" s="4" t="inlineStr">
         <is>
-          <t>金貨</t>
+          <t>金币</t>
         </is>
       </c>
       <c r="I1303" t="inlineStr">
@@ -49889,7 +49889,7 @@
       </c>
       <c r="G1304" s="4" t="inlineStr">
         <is>
-          <t>突破素材パック</t>
+          <t>突破材料包</t>
         </is>
       </c>
       <c r="I1304" t="inlineStr">
@@ -49929,7 +49929,7 @@
       </c>
       <c r="G1306" s="1" t="inlineStr">
         <is>
-          <t>ハロウィンアイコン*1</t>
+          <t>万圣节图标*1</t>
         </is>
       </c>
       <c r="H1306" t="inlineStr">
@@ -49971,7 +49971,7 @@
       </c>
       <c r="G1307" s="1" t="inlineStr">
         <is>
-          <t>ハロウィンフレーム*1</t>
+          <t>万圣节框架*1</t>
         </is>
       </c>
       <c r="H1307" t="inlineStr">
@@ -50013,7 +50013,7 @@
       </c>
       <c r="G1308" s="1" t="inlineStr">
         <is>
-          <t>ハロウィン称号*1</t>
+          <t>万圣节称号*1</t>
         </is>
       </c>
       <c r="H1308" t="inlineStr">
@@ -50055,7 +50055,7 @@
       </c>
       <c r="G1309" s="5" t="inlineStr">
         <is>
-          <t>ハロウィン立絵*1</t>
+          <t>万圣节立画*1</t>
         </is>
       </c>
       <c r="I1309" t="inlineStr">
@@ -50092,7 +50092,7 @@
       </c>
       <c r="G1310" s="1" t="inlineStr">
         <is>
-          <t>ハロウィンスキン*1</t>
+          <t>万圣节皮肤*1</t>
         </is>
       </c>
       <c r="I1310" t="inlineStr">
@@ -50129,7 +50129,7 @@
       </c>
       <c r="G1311" s="1" t="inlineStr">
         <is>
-          <t>ハロウィン金貨パック*1</t>
+          <t>万圣节金币包*1</t>
         </is>
       </c>
       <c r="H1311" t="inlineStr">
@@ -50171,7 +50171,7 @@
       </c>
       <c r="G1312" s="1" t="inlineStr">
         <is>
-          <t>ハロウィンダイヤギフト*1</t>
+          <t>万圣节钻石礼品*1</t>
         </is>
       </c>
       <c r="H1312" t="inlineStr">
@@ -50213,7 +50213,7 @@
       </c>
       <c r="G1313" s="1" t="inlineStr">
         <is>
-          <t>スパイ万能欠片*1</t>
+          <t>间谍万能碎片*1</t>
         </is>
       </c>
       <c r="H1313" t="inlineStr">
@@ -50255,7 +50255,7 @@
       </c>
       <c r="G1314" s="5" t="inlineStr">
         <is>
-          <t>装飾星アップアイテム</t>
+          <t>装饰星星项目</t>
         </is>
       </c>
       <c r="H1314" t="inlineStr">
@@ -50297,7 +50297,7 @@
       </c>
       <c r="G1315" s="1" t="inlineStr">
         <is>
-          <t>銀の首飾り*1</t>
+          <t>银项链*1</t>
         </is>
       </c>
       <c r="H1315" t="inlineStr">
@@ -50339,7 +50339,7 @@
       </c>
       <c r="G1316" s="1" t="inlineStr">
         <is>
-          <t>紫·強化*1</t>
+          <t>紫色强化*1</t>
         </is>
       </c>
       <c r="H1316" t="inlineStr">
@@ -50507,7 +50507,7 @@
       </c>
       <c r="G1320" s="1" t="inlineStr">
         <is>
-          <t>エネルギーの薬*5</t>
+          <t>能量药物*5</t>
         </is>
       </c>
       <c r="H1320" t="inlineStr">
@@ -50549,7 +50549,7 @@
       </c>
       <c r="G1321" s="1" t="inlineStr">
         <is>
-          <t>金貨*5万</t>
+          <t>金币5万</t>
         </is>
       </c>
       <c r="H1321" t="inlineStr">
